--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3156,10 +3156,10 @@
         <v>47578.24</v>
       </c>
       <c r="E54" s="0" t="n">
-        <v>45839.36</v>
+        <v>45398.43</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>46184.85</v>
+        <v>45862.52</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>47578.24</v>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N656"/>
+  <dimension ref="A1:N657"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27503,22 +27503,22 @@
       <c r="A656" s="62" t="n">
         <v>46276</v>
       </c>
-      <c r="B656" t="n">
+      <c r="B656" s="0" t="n">
         <v>46651.21</v>
       </c>
-      <c r="C656" t="n">
+      <c r="C656" s="0" t="n">
         <v>46651.21</v>
       </c>
-      <c r="D656" t="n">
+      <c r="D656" s="0" t="n">
         <v>45942.44</v>
       </c>
-      <c r="E656" t="n">
+      <c r="E656" s="0" t="n">
         <v>46184.85</v>
       </c>
-      <c r="F656" t="n">
+      <c r="F656" s="0" t="n">
         <v>-755.64</v>
       </c>
-      <c r="G656" t="n">
+      <c r="G656" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H656" s="55">
@@ -27531,6 +27531,41 @@
       </c>
       <c r="J656" s="34">
         <f>AVERAGE(I655:I656)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="62" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B657" t="n">
+        <v>46010.74</v>
+      </c>
+      <c r="C657" t="n">
+        <v>46050.24</v>
+      </c>
+      <c r="D657" t="n">
+        <v>45398.43</v>
+      </c>
+      <c r="E657" t="n">
+        <v>45862.52</v>
+      </c>
+      <c r="F657" t="n">
+        <v>-322.33</v>
+      </c>
+      <c r="G657" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H657" s="55">
+        <f>E657-G657</f>
+        <v/>
+      </c>
+      <c r="I657" s="34">
+        <f>H657/1000</f>
+        <v/>
+      </c>
+      <c r="J657" s="34">
+        <f>AVERAGE(I656:I657)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3159,7 +3159,7 @@
         <v>45398.43</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>45862.52</v>
+        <v>45511.49</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>47578.24</v>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N657"/>
+  <dimension ref="A1:N658"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27538,22 +27538,22 @@
       <c r="A657" s="62" t="n">
         <v>46279</v>
       </c>
-      <c r="B657" t="n">
+      <c r="B657" s="0" t="n">
         <v>46010.74</v>
       </c>
-      <c r="C657" t="n">
+      <c r="C657" s="0" t="n">
         <v>46050.24</v>
       </c>
-      <c r="D657" t="n">
+      <c r="D657" s="0" t="n">
         <v>45398.43</v>
       </c>
-      <c r="E657" t="n">
+      <c r="E657" s="0" t="n">
         <v>45862.52</v>
       </c>
-      <c r="F657" t="n">
+      <c r="F657" s="0" t="n">
         <v>-322.33</v>
       </c>
-      <c r="G657" t="n">
+      <c r="G657" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H657" s="55">
@@ -27566,6 +27566,41 @@
       </c>
       <c r="J657" s="34">
         <f>AVERAGE(I656:I657)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="62" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B658" t="n">
+        <v>45847.27</v>
+      </c>
+      <c r="C658" t="n">
+        <v>46009.85</v>
+      </c>
+      <c r="D658" t="n">
+        <v>45491.97</v>
+      </c>
+      <c r="E658" t="n">
+        <v>45511.49</v>
+      </c>
+      <c r="F658" t="n">
+        <v>-351.03</v>
+      </c>
+      <c r="G658" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H658" s="55">
+        <f>E658-G658</f>
+        <v/>
+      </c>
+      <c r="I658" s="34">
+        <f>H658/1000</f>
+        <v/>
+      </c>
+      <c r="J658" s="34">
+        <f>AVERAGE(I657:I658)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3159,7 +3159,7 @@
         <v>45398.43</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>45511.49</v>
+        <v>45848.9</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>47578.24</v>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N658"/>
+  <dimension ref="A1:N659"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27573,22 +27573,22 @@
       <c r="A658" s="62" t="n">
         <v>46280</v>
       </c>
-      <c r="B658" t="n">
+      <c r="B658" s="0" t="n">
         <v>45847.27</v>
       </c>
-      <c r="C658" t="n">
+      <c r="C658" s="0" t="n">
         <v>46009.85</v>
       </c>
-      <c r="D658" t="n">
+      <c r="D658" s="0" t="n">
         <v>45491.97</v>
       </c>
-      <c r="E658" t="n">
+      <c r="E658" s="0" t="n">
         <v>45511.49</v>
       </c>
-      <c r="F658" t="n">
+      <c r="F658" s="0" t="n">
         <v>-351.03</v>
       </c>
-      <c r="G658" t="n">
+      <c r="G658" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H658" s="55">
@@ -27601,6 +27601,41 @@
       </c>
       <c r="J658" s="34">
         <f>AVERAGE(I657:I658)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="62" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B659" t="n">
+        <v>45546.56</v>
+      </c>
+      <c r="C659" t="n">
+        <v>46077.82</v>
+      </c>
+      <c r="D659" t="n">
+        <v>45546.56</v>
+      </c>
+      <c r="E659" t="n">
+        <v>45848.9</v>
+      </c>
+      <c r="F659" t="n">
+        <v>337.41</v>
+      </c>
+      <c r="G659" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H659" s="55">
+        <f>E659-G659</f>
+        <v/>
+      </c>
+      <c r="I659" s="34">
+        <f>H659/1000</f>
+        <v/>
+      </c>
+      <c r="J659" s="34">
+        <f>AVERAGE(I658:I659)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3159,7 +3159,7 @@
         <v>45398.43</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>45848.9</v>
+        <v>46288</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>47578.24</v>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N659"/>
+  <dimension ref="A1:N660"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27608,22 +27608,22 @@
       <c r="A659" s="62" t="n">
         <v>46281</v>
       </c>
-      <c r="B659" t="n">
+      <c r="B659" s="0" t="n">
         <v>45546.56</v>
       </c>
-      <c r="C659" t="n">
+      <c r="C659" s="0" t="n">
         <v>46077.82</v>
       </c>
-      <c r="D659" t="n">
+      <c r="D659" s="0" t="n">
         <v>45546.56</v>
       </c>
-      <c r="E659" t="n">
+      <c r="E659" s="0" t="n">
         <v>45848.9</v>
       </c>
-      <c r="F659" t="n">
+      <c r="F659" s="0" t="n">
         <v>337.41</v>
       </c>
-      <c r="G659" t="n">
+      <c r="G659" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H659" s="55">
@@ -27636,6 +27636,41 @@
       </c>
       <c r="J659" s="34">
         <f>AVERAGE(I658:I659)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="62" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B660" t="n">
+        <v>45936.11</v>
+      </c>
+      <c r="C660" t="n">
+        <v>46874.84</v>
+      </c>
+      <c r="D660" t="n">
+        <v>45936.11</v>
+      </c>
+      <c r="E660" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F660" t="n">
+        <v>439.1</v>
+      </c>
+      <c r="G660" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H660" s="55">
+        <f>E660-G660</f>
+        <v/>
+      </c>
+      <c r="I660" s="34">
+        <f>H660/1000</f>
+        <v/>
+      </c>
+      <c r="J660" s="34">
+        <f>AVERAGE(I659:I660)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3159,7 +3159,7 @@
         <v>45398.43</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>46288</v>
+        <v>47180.75</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>47578.24</v>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N660"/>
+  <dimension ref="A1:N661"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27643,22 +27643,22 @@
       <c r="A660" s="62" t="n">
         <v>46282</v>
       </c>
-      <c r="B660" t="n">
+      <c r="B660" s="0" t="n">
         <v>45936.11</v>
       </c>
-      <c r="C660" t="n">
+      <c r="C660" s="0" t="n">
         <v>46874.84</v>
       </c>
-      <c r="D660" t="n">
+      <c r="D660" s="0" t="n">
         <v>45936.11</v>
       </c>
-      <c r="E660" t="n">
+      <c r="E660" s="0" t="n">
         <v>46288</v>
       </c>
-      <c r="F660" t="n">
+      <c r="F660" s="0" t="n">
         <v>439.1</v>
       </c>
-      <c r="G660" t="n">
+      <c r="G660" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H660" s="55">
@@ -27671,6 +27671,41 @@
       </c>
       <c r="J660" s="34">
         <f>AVERAGE(I659:I660)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="62" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B661" t="n">
+        <v>46449.56</v>
+      </c>
+      <c r="C661" t="n">
+        <v>47180.75</v>
+      </c>
+      <c r="D661" t="n">
+        <v>46449.56</v>
+      </c>
+      <c r="E661" t="n">
+        <v>47180.75</v>
+      </c>
+      <c r="F661" t="n">
+        <v>892.75</v>
+      </c>
+      <c r="G661" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H661" s="55">
+        <f>E661-G661</f>
+        <v/>
+      </c>
+      <c r="I661" s="34">
+        <f>H661/1000</f>
+        <v/>
+      </c>
+      <c r="J661" s="34">
+        <f>AVERAGE(I660:I661)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,28 +3147,28 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>47578.24</v>
+        <v>47750.98</v>
       </c>
       <c r="E54" s="0" t="n">
         <v>45398.43</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>47180.75</v>
+        <v>47718.84</v>
       </c>
       <c r="G54" s="0" t="n">
-        <v>47578.24</v>
+        <v>47750.98</v>
       </c>
       <c r="H54" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="I54" s="0" t="n">
-        <v>45179.33</v>
+        <v>45265.7</v>
       </c>
       <c r="J54" s="0" t="n">
         <v>43390.075</v>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="55">
       <c r="J55" s="0" t="n">
-        <v>45179.33</v>
+        <v>45265.7</v>
       </c>
     </row>
   </sheetData>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N661"/>
+  <dimension ref="A1:N662"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27678,22 +27678,22 @@
       <c r="A661" s="62" t="n">
         <v>46283</v>
       </c>
-      <c r="B661" t="n">
+      <c r="B661" s="0" t="n">
         <v>46449.56</v>
       </c>
-      <c r="C661" t="n">
+      <c r="C661" s="0" t="n">
         <v>47180.75</v>
       </c>
-      <c r="D661" t="n">
+      <c r="D661" s="0" t="n">
         <v>46449.56</v>
       </c>
-      <c r="E661" t="n">
+      <c r="E661" s="0" t="n">
         <v>47180.75</v>
       </c>
-      <c r="F661" t="n">
+      <c r="F661" s="0" t="n">
         <v>892.75</v>
       </c>
-      <c r="G661" t="n">
+      <c r="G661" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H661" s="55">
@@ -27706,6 +27706,41 @@
       </c>
       <c r="J661" s="34">
         <f>AVERAGE(I660:I661)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="62" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B662" t="n">
+        <v>47207.3</v>
+      </c>
+      <c r="C662" t="n">
+        <v>47750.98</v>
+      </c>
+      <c r="D662" t="n">
+        <v>47207.3</v>
+      </c>
+      <c r="E662" t="n">
+        <v>47718.84</v>
+      </c>
+      <c r="F662" t="n">
+        <v>538.09</v>
+      </c>
+      <c r="G662" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H662" s="55">
+        <f>E662-G662</f>
+        <v/>
+      </c>
+      <c r="I662" s="34">
+        <f>H662/1000</f>
+        <v/>
+      </c>
+      <c r="J662" s="34">
+        <f>AVERAGE(I661:I662)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,28 +3147,28 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>47750.98</v>
+        <v>48601.53</v>
       </c>
       <c r="E54" s="0" t="n">
         <v>45398.43</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>47718.84</v>
+        <v>47800.17</v>
       </c>
       <c r="G54" s="0" t="n">
-        <v>47750.98</v>
+        <v>48601.53</v>
       </c>
       <c r="H54" s="0" t="n">
         <v>42780.42</v>
       </c>
       <c r="I54" s="0" t="n">
-        <v>45265.7</v>
+        <v>45690.975</v>
       </c>
       <c r="J54" s="0" t="n">
         <v>43390.075</v>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="55">
       <c r="J55" s="0" t="n">
-        <v>45265.7</v>
+        <v>45690.975</v>
       </c>
     </row>
   </sheetData>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N662"/>
+  <dimension ref="A1:N663"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27713,22 +27713,22 @@
       <c r="A662" s="62" t="n">
         <v>46286</v>
       </c>
-      <c r="B662" t="n">
+      <c r="B662" s="0" t="n">
         <v>47207.3</v>
       </c>
-      <c r="C662" t="n">
+      <c r="C662" s="0" t="n">
         <v>47750.98</v>
       </c>
-      <c r="D662" t="n">
+      <c r="D662" s="0" t="n">
         <v>47207.3</v>
       </c>
-      <c r="E662" t="n">
+      <c r="E662" s="0" t="n">
         <v>47718.84</v>
       </c>
-      <c r="F662" t="n">
+      <c r="F662" s="0" t="n">
         <v>538.09</v>
       </c>
-      <c r="G662" t="n">
+      <c r="G662" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H662" s="55">
@@ -27741,6 +27741,41 @@
       </c>
       <c r="J662" s="34">
         <f>AVERAGE(I661:I662)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="62" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B663" t="n">
+        <v>47981.04</v>
+      </c>
+      <c r="C663" t="n">
+        <v>48601.53</v>
+      </c>
+      <c r="D663" t="n">
+        <v>47800.17</v>
+      </c>
+      <c r="E663" t="n">
+        <v>47800.17</v>
+      </c>
+      <c r="F663" t="n">
+        <v>81.33</v>
+      </c>
+      <c r="G663" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H663" s="55">
+        <f>E663-G663</f>
+        <v/>
+      </c>
+      <c r="I663" s="34">
+        <f>H663/1000</f>
+        <v/>
+      </c>
+      <c r="J663" s="34">
+        <f>AVERAGE(I662:I663)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3159,7 +3159,7 @@
         <v>45398.43</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>47800.17</v>
+        <v>48157.29</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>48601.53</v>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N663"/>
+  <dimension ref="A1:N664"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27748,22 +27748,22 @@
       <c r="A663" s="62" t="n">
         <v>46287</v>
       </c>
-      <c r="B663" t="n">
+      <c r="B663" s="0" t="n">
         <v>47981.04</v>
       </c>
-      <c r="C663" t="n">
+      <c r="C663" s="0" t="n">
         <v>48601.53</v>
       </c>
-      <c r="D663" t="n">
+      <c r="D663" s="0" t="n">
         <v>47800.17</v>
       </c>
-      <c r="E663" t="n">
+      <c r="E663" s="0" t="n">
         <v>47800.17</v>
       </c>
-      <c r="F663" t="n">
+      <c r="F663" s="0" t="n">
         <v>81.33</v>
       </c>
-      <c r="G663" t="n">
+      <c r="G663" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H663" s="55">
@@ -27776,6 +27776,41 @@
       </c>
       <c r="J663" s="34">
         <f>AVERAGE(I662:I663)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="62" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B664" t="n">
+        <v>47894.77</v>
+      </c>
+      <c r="C664" t="n">
+        <v>48341.56</v>
+      </c>
+      <c r="D664" t="n">
+        <v>47894.77</v>
+      </c>
+      <c r="E664" t="n">
+        <v>48157.29</v>
+      </c>
+      <c r="F664" t="n">
+        <v>357.12</v>
+      </c>
+      <c r="G664" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H664" s="55">
+        <f>E664-G664</f>
+        <v/>
+      </c>
+      <c r="I664" s="34">
+        <f>H664/1000</f>
+        <v/>
+      </c>
+      <c r="J664" s="34">
+        <f>AVERAGE(I663:I664)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,11 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -27783,22 +27782,22 @@
       <c r="A664" s="62" t="n">
         <v>46288</v>
       </c>
-      <c r="B664" t="n">
+      <c r="B664" s="0" t="n">
         <v>47894.77</v>
       </c>
-      <c r="C664" t="n">
+      <c r="C664" s="0" t="n">
         <v>48341.56</v>
       </c>
-      <c r="D664" t="n">
+      <c r="D664" s="0" t="n">
         <v>47894.77</v>
       </c>
-      <c r="E664" t="n">
+      <c r="E664" s="0" t="n">
         <v>48157.29</v>
       </c>
-      <c r="F664" t="n">
+      <c r="F664" s="0" t="n">
         <v>357.12</v>
       </c>
-      <c r="G664" t="n">
+      <c r="G664" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H664" s="55">

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -3146,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3158,7 +3159,7 @@
         <v>45398.43</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>48157.29</v>
+        <v>48024.6</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>48601.53</v>
@@ -3190,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N664"/>
+  <dimension ref="A1:N665"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27813,6 +27814,41 @@
         <v/>
       </c>
     </row>
+    <row r="665">
+      <c r="A665" s="62" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B665" t="n">
+        <v>48075.39</v>
+      </c>
+      <c r="C665" t="n">
+        <v>48117.54</v>
+      </c>
+      <c r="D665" t="n">
+        <v>47754.72</v>
+      </c>
+      <c r="E665" t="n">
+        <v>48024.6</v>
+      </c>
+      <c r="F665" t="n">
+        <v>-132.69</v>
+      </c>
+      <c r="G665" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H665" s="55">
+        <f>E665-G665</f>
+        <v/>
+      </c>
+      <c r="I665" s="34">
+        <f>H665/1000</f>
+        <v/>
+      </c>
+      <c r="J665" s="34">
+        <f>AVERAGE(I664:I665)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,11 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -27818,22 +27817,22 @@
       <c r="A665" s="62" t="n">
         <v>46289</v>
       </c>
-      <c r="B665" t="n">
+      <c r="B665" s="0" t="n">
         <v>48075.39</v>
       </c>
-      <c r="C665" t="n">
+      <c r="C665" s="0" t="n">
         <v>48117.54</v>
       </c>
-      <c r="D665" t="n">
+      <c r="D665" s="0" t="n">
         <v>47754.72</v>
       </c>
-      <c r="E665" t="n">
+      <c r="E665" s="0" t="n">
         <v>48024.6</v>
       </c>
-      <c r="F665" t="n">
+      <c r="F665" s="0" t="n">
         <v>-132.69</v>
       </c>
-      <c r="G665" t="n">
+      <c r="G665" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H665" s="55">

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -3146,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3158,7 +3159,7 @@
         <v>45398.43</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>48024.6</v>
+        <v>47631.96</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>48601.53</v>
@@ -3190,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N665"/>
+  <dimension ref="A1:N666"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27848,6 +27849,41 @@
         <v/>
       </c>
     </row>
+    <row r="666">
+      <c r="A666" s="62" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B666" t="n">
+        <v>47873.89</v>
+      </c>
+      <c r="C666" t="n">
+        <v>48045.13</v>
+      </c>
+      <c r="D666" t="n">
+        <v>47573.09</v>
+      </c>
+      <c r="E666" t="n">
+        <v>47631.96</v>
+      </c>
+      <c r="F666" t="n">
+        <v>-392.64</v>
+      </c>
+      <c r="G666" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H666" s="55">
+        <f>E666-G666</f>
+        <v/>
+      </c>
+      <c r="I666" s="34">
+        <f>H666/1000</f>
+        <v/>
+      </c>
+      <c r="J666" s="34">
+        <f>AVERAGE(I665:I666)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="B54" s="0" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>46177.11</v>
@@ -3159,7 +3159,7 @@
         <v>45398.43</v>
       </c>
       <c r="F54" s="0" t="n">
-        <v>47631.96</v>
+        <v>47940.13</v>
       </c>
       <c r="G54" s="0" t="n">
         <v>48601.53</v>
@@ -3191,7 +3191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N666"/>
+  <dimension ref="A1:N667"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27853,22 +27853,22 @@
       <c r="A666" s="62" t="n">
         <v>46294</v>
       </c>
-      <c r="B666" t="n">
+      <c r="B666" s="0" t="n">
         <v>47873.89</v>
       </c>
-      <c r="C666" t="n">
+      <c r="C666" s="0" t="n">
         <v>48045.13</v>
       </c>
-      <c r="D666" t="n">
+      <c r="D666" s="0" t="n">
         <v>47573.09</v>
       </c>
-      <c r="E666" t="n">
+      <c r="E666" s="0" t="n">
         <v>47631.96</v>
       </c>
-      <c r="F666" t="n">
+      <c r="F666" s="0" t="n">
         <v>-392.64</v>
       </c>
-      <c r="G666" t="n">
+      <c r="G666" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H666" s="55">
@@ -27881,6 +27881,41 @@
       </c>
       <c r="J666" s="34">
         <f>AVERAGE(I665:I666)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="62" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B667" t="n">
+        <v>47767.49</v>
+      </c>
+      <c r="C667" t="n">
+        <v>48379.71</v>
+      </c>
+      <c r="D667" t="n">
+        <v>47767.49</v>
+      </c>
+      <c r="E667" t="n">
+        <v>47940.13</v>
+      </c>
+      <c r="F667" t="n">
+        <v>308.17</v>
+      </c>
+      <c r="G667" t="n">
+        <v>43390.075</v>
+      </c>
+      <c r="H667" s="55">
+        <f>E667-G667</f>
+        <v/>
+      </c>
+      <c r="I667" s="34">
+        <f>H667/1000</f>
+        <v/>
+      </c>
+      <c r="J667" s="34">
+        <f>AVERAGE(I666:I667)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -740,7 +740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="6.5" defaultRowHeight="16.5"/>
   <cols>
     <col width="5.875" customWidth="1" style="1" min="1" max="1"/>
@@ -3175,8 +3175,42 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>26M10</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>47961.98</v>
+      </c>
+      <c r="D55" t="n">
+        <v>48353.49</v>
+      </c>
+      <c r="E55" t="n">
+        <v>47893.42</v>
+      </c>
+      <c r="F55" t="n">
+        <v>48353.49</v>
+      </c>
+      <c r="G55" t="n">
+        <v>48601.53</v>
+      </c>
+      <c r="H55" t="n">
+        <v>45398.43</v>
+      </c>
+      <c r="I55" t="n">
+        <v>46999.98</v>
+      </c>
       <c r="J55" s="0" t="n">
         <v>45690.975</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="J56" t="n">
+        <v>46999.98</v>
       </c>
     </row>
   </sheetData>
@@ -3191,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N667"/>
+  <dimension ref="A1:N668"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27888,22 +27922,22 @@
       <c r="A667" s="62" t="n">
         <v>46295</v>
       </c>
-      <c r="B667" t="n">
+      <c r="B667" s="0" t="n">
         <v>47767.49</v>
       </c>
-      <c r="C667" t="n">
+      <c r="C667" s="0" t="n">
         <v>48379.71</v>
       </c>
-      <c r="D667" t="n">
+      <c r="D667" s="0" t="n">
         <v>47767.49</v>
       </c>
-      <c r="E667" t="n">
+      <c r="E667" s="0" t="n">
         <v>47940.13</v>
       </c>
-      <c r="F667" t="n">
+      <c r="F667" s="0" t="n">
         <v>308.17</v>
       </c>
-      <c r="G667" t="n">
+      <c r="G667" s="0" t="n">
         <v>43390.075</v>
       </c>
       <c r="H667" s="55">
@@ -27916,6 +27950,41 @@
       </c>
       <c r="J667" s="34">
         <f>AVERAGE(I666:I667)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="62" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B668" t="n">
+        <v>47961.98</v>
+      </c>
+      <c r="C668" t="n">
+        <v>48353.49</v>
+      </c>
+      <c r="D668" t="n">
+        <v>47893.42</v>
+      </c>
+      <c r="E668" t="n">
+        <v>48353.49</v>
+      </c>
+      <c r="F668" t="n">
+        <v>413.36</v>
+      </c>
+      <c r="G668" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H668" s="55">
+        <f>E668-G668</f>
+        <v/>
+      </c>
+      <c r="I668" s="34">
+        <f>H668/1000</f>
+        <v/>
+      </c>
+      <c r="J668" s="34">
+        <f>AVERAGE(I667:I668)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3175,33 +3175,33 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="0" t="inlineStr">
         <is>
           <t>26M10</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="n">
+      <c r="B55" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="0" t="n">
         <v>47961.98</v>
       </c>
-      <c r="D55" t="n">
-        <v>48353.49</v>
-      </c>
-      <c r="E55" t="n">
+      <c r="D55" s="0" t="n">
+        <v>48491.62</v>
+      </c>
+      <c r="E55" s="0" t="n">
         <v>47893.42</v>
       </c>
-      <c r="F55" t="n">
-        <v>48353.49</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="F55" s="0" t="n">
+        <v>48475.74</v>
+      </c>
+      <c r="G55" s="0" t="n">
         <v>48601.53</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="0" t="n">
         <v>45398.43</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55" s="0" t="n">
         <v>46999.98</v>
       </c>
       <c r="J55" s="0" t="n">
@@ -3209,7 +3209,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="J56" t="n">
+      <c r="J56" s="0" t="n">
         <v>46999.98</v>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N668"/>
+  <dimension ref="A1:N669"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27957,22 +27957,22 @@
       <c r="A668" s="62" t="n">
         <v>46296</v>
       </c>
-      <c r="B668" t="n">
+      <c r="B668" s="0" t="n">
         <v>47961.98</v>
       </c>
-      <c r="C668" t="n">
+      <c r="C668" s="0" t="n">
         <v>48353.49</v>
       </c>
-      <c r="D668" t="n">
+      <c r="D668" s="0" t="n">
         <v>47893.42</v>
       </c>
-      <c r="E668" t="n">
+      <c r="E668" s="0" t="n">
         <v>48353.49</v>
       </c>
-      <c r="F668" t="n">
+      <c r="F668" s="0" t="n">
         <v>413.36</v>
       </c>
-      <c r="G668" t="n">
+      <c r="G668" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H668" s="55">
@@ -27985,6 +27985,41 @@
       </c>
       <c r="J668" s="34">
         <f>AVERAGE(I667:I668)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="62" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B669" t="n">
+        <v>48390.65</v>
+      </c>
+      <c r="C669" t="n">
+        <v>48491.62</v>
+      </c>
+      <c r="D669" t="n">
+        <v>48205.81</v>
+      </c>
+      <c r="E669" t="n">
+        <v>48475.74</v>
+      </c>
+      <c r="F669" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="G669" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H669" s="55">
+        <f>E669-G669</f>
+        <v/>
+      </c>
+      <c r="I669" s="34">
+        <f>H669/1000</f>
+        <v/>
+      </c>
+      <c r="J669" s="34">
+        <f>AVERAGE(I668:I669)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,28 +3181,28 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>48491.62</v>
+        <v>49770.66</v>
       </c>
       <c r="E55" s="0" t="n">
         <v>47893.42</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>48475.74</v>
+        <v>49712.04</v>
       </c>
       <c r="G55" s="0" t="n">
-        <v>48601.53</v>
+        <v>49770.66</v>
       </c>
       <c r="H55" s="0" t="n">
         <v>45398.43</v>
       </c>
       <c r="I55" s="0" t="n">
-        <v>46999.98</v>
+        <v>47584.545</v>
       </c>
       <c r="J55" s="0" t="n">
         <v>45690.975</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="56">
       <c r="J56" s="0" t="n">
-        <v>46999.98</v>
+        <v>47584.545</v>
       </c>
     </row>
   </sheetData>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N669"/>
+  <dimension ref="A1:N670"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -27992,22 +27992,22 @@
       <c r="A669" s="62" t="n">
         <v>46297</v>
       </c>
-      <c r="B669" t="n">
+      <c r="B669" s="0" t="n">
         <v>48390.65</v>
       </c>
-      <c r="C669" t="n">
+      <c r="C669" s="0" t="n">
         <v>48491.62</v>
       </c>
-      <c r="D669" t="n">
+      <c r="D669" s="0" t="n">
         <v>48205.81</v>
       </c>
-      <c r="E669" t="n">
+      <c r="E669" s="0" t="n">
         <v>48475.74</v>
       </c>
-      <c r="F669" t="n">
+      <c r="F669" s="0" t="n">
         <v>122.25</v>
       </c>
-      <c r="G669" t="n">
+      <c r="G669" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H669" s="55">
@@ -28020,6 +28020,41 @@
       </c>
       <c r="J669" s="34">
         <f>AVERAGE(I668:I669)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="62" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B670" t="n">
+        <v>48574.95</v>
+      </c>
+      <c r="C670" t="n">
+        <v>49770.66</v>
+      </c>
+      <c r="D670" t="n">
+        <v>48574.95</v>
+      </c>
+      <c r="E670" t="n">
+        <v>49712.04</v>
+      </c>
+      <c r="F670" t="n">
+        <v>1236.3</v>
+      </c>
+      <c r="G670" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H670" s="55">
+        <f>E670-G670</f>
+        <v/>
+      </c>
+      <c r="I670" s="34">
+        <f>H670/1000</f>
+        <v/>
+      </c>
+      <c r="J670" s="34">
+        <f>AVERAGE(I669:I670)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,28 +3181,28 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>49770.66</v>
+        <v>49968.92</v>
       </c>
       <c r="E55" s="0" t="n">
         <v>47893.42</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>49712.04</v>
+        <v>49822.55</v>
       </c>
       <c r="G55" s="0" t="n">
-        <v>49770.66</v>
+        <v>49968.92</v>
       </c>
       <c r="H55" s="0" t="n">
         <v>45398.43</v>
       </c>
       <c r="I55" s="0" t="n">
-        <v>47584.545</v>
+        <v>47683.675</v>
       </c>
       <c r="J55" s="0" t="n">
         <v>45690.975</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="56">
       <c r="J56" s="0" t="n">
-        <v>47584.545</v>
+        <v>47683.675</v>
       </c>
     </row>
   </sheetData>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N670"/>
+  <dimension ref="A1:N671"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28027,22 +28027,22 @@
       <c r="A670" s="62" t="n">
         <v>46300</v>
       </c>
-      <c r="B670" t="n">
+      <c r="B670" s="0" t="n">
         <v>48574.95</v>
       </c>
-      <c r="C670" t="n">
+      <c r="C670" s="0" t="n">
         <v>49770.66</v>
       </c>
-      <c r="D670" t="n">
+      <c r="D670" s="0" t="n">
         <v>48574.95</v>
       </c>
-      <c r="E670" t="n">
+      <c r="E670" s="0" t="n">
         <v>49712.04</v>
       </c>
-      <c r="F670" t="n">
+      <c r="F670" s="0" t="n">
         <v>1236.3</v>
       </c>
-      <c r="G670" t="n">
+      <c r="G670" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H670" s="55">
@@ -28055,6 +28055,41 @@
       </c>
       <c r="J670" s="34">
         <f>AVERAGE(I669:I670)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="62" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B671" t="n">
+        <v>49736.37</v>
+      </c>
+      <c r="C671" t="n">
+        <v>49968.92</v>
+      </c>
+      <c r="D671" t="n">
+        <v>49479.69</v>
+      </c>
+      <c r="E671" t="n">
+        <v>49822.55</v>
+      </c>
+      <c r="F671" t="n">
+        <v>110.51</v>
+      </c>
+      <c r="G671" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H671" s="55">
+        <f>E671-G671</f>
+        <v/>
+      </c>
+      <c r="I671" s="34">
+        <f>H671/1000</f>
+        <v/>
+      </c>
+      <c r="J671" s="34">
+        <f>AVERAGE(I670:I671)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3193,7 +3193,7 @@
         <v>47893.42</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>49822.55</v>
+        <v>49806.37</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N671"/>
+  <dimension ref="A1:N672"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28062,22 +28062,22 @@
       <c r="A671" s="62" t="n">
         <v>46301</v>
       </c>
-      <c r="B671" t="n">
+      <c r="B671" s="0" t="n">
         <v>49736.37</v>
       </c>
-      <c r="C671" t="n">
+      <c r="C671" s="0" t="n">
         <v>49968.92</v>
       </c>
-      <c r="D671" t="n">
+      <c r="D671" s="0" t="n">
         <v>49479.69</v>
       </c>
-      <c r="E671" t="n">
+      <c r="E671" s="0" t="n">
         <v>49822.55</v>
       </c>
-      <c r="F671" t="n">
+      <c r="F671" s="0" t="n">
         <v>110.51</v>
       </c>
-      <c r="G671" t="n">
+      <c r="G671" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H671" s="55">
@@ -28090,6 +28090,41 @@
       </c>
       <c r="J671" s="34">
         <f>AVERAGE(I670:I671)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="62" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B672" t="n">
+        <v>49857.32</v>
+      </c>
+      <c r="C672" t="n">
+        <v>49966.89</v>
+      </c>
+      <c r="D672" t="n">
+        <v>49567.52</v>
+      </c>
+      <c r="E672" t="n">
+        <v>49806.37</v>
+      </c>
+      <c r="F672" t="n">
+        <v>-16.18</v>
+      </c>
+      <c r="G672" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H672" s="55">
+        <f>E672-G672</f>
+        <v/>
+      </c>
+      <c r="I672" s="34">
+        <f>H672/1000</f>
+        <v/>
+      </c>
+      <c r="J672" s="34">
+        <f>AVERAGE(I671:I672)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3193,7 +3193,7 @@
         <v>47893.42</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>49806.37</v>
+        <v>49313.44</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N672"/>
+  <dimension ref="A1:N673"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28097,22 +28097,22 @@
       <c r="A672" s="62" t="n">
         <v>46302</v>
       </c>
-      <c r="B672" t="n">
+      <c r="B672" s="0" t="n">
         <v>49857.32</v>
       </c>
-      <c r="C672" t="n">
+      <c r="C672" s="0" t="n">
         <v>49966.89</v>
       </c>
-      <c r="D672" t="n">
+      <c r="D672" s="0" t="n">
         <v>49567.52</v>
       </c>
-      <c r="E672" t="n">
+      <c r="E672" s="0" t="n">
         <v>49806.37</v>
       </c>
-      <c r="F672" t="n">
+      <c r="F672" s="0" t="n">
         <v>-16.18</v>
       </c>
-      <c r="G672" t="n">
+      <c r="G672" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H672" s="55">
@@ -28125,6 +28125,41 @@
       </c>
       <c r="J672" s="34">
         <f>AVERAGE(I671:I672)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="62" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B673" t="n">
+        <v>49783.06</v>
+      </c>
+      <c r="C673" t="n">
+        <v>49783.06</v>
+      </c>
+      <c r="D673" t="n">
+        <v>49189.77</v>
+      </c>
+      <c r="E673" t="n">
+        <v>49313.44</v>
+      </c>
+      <c r="F673" t="n">
+        <v>-492.93</v>
+      </c>
+      <c r="G673" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H673" s="55">
+        <f>E673-G673</f>
+        <v/>
+      </c>
+      <c r="I673" s="34">
+        <f>H673/1000</f>
+        <v/>
+      </c>
+      <c r="J673" s="34">
+        <f>AVERAGE(I672:I673)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,11 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -28132,22 +28131,22 @@
       <c r="A673" s="62" t="n">
         <v>46303</v>
       </c>
-      <c r="B673" t="n">
+      <c r="B673" s="0" t="n">
         <v>49783.06</v>
       </c>
-      <c r="C673" t="n">
+      <c r="C673" s="0" t="n">
         <v>49783.06</v>
       </c>
-      <c r="D673" t="n">
+      <c r="D673" s="0" t="n">
         <v>49189.77</v>
       </c>
-      <c r="E673" t="n">
+      <c r="E673" s="0" t="n">
         <v>49313.44</v>
       </c>
-      <c r="F673" t="n">
+      <c r="F673" s="0" t="n">
         <v>-492.93</v>
       </c>
-      <c r="G673" t="n">
+      <c r="G673" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H673" s="55">

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -3180,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3192,7 +3193,7 @@
         <v>47893.42</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>49313.44</v>
+        <v>49301.96</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3224,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N673"/>
+  <dimension ref="A1:N674"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28162,6 +28163,41 @@
         <v/>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" s="62" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B674" t="n">
+        <v>49272.08</v>
+      </c>
+      <c r="C674" t="n">
+        <v>49412.9</v>
+      </c>
+      <c r="D674" t="n">
+        <v>48768.82</v>
+      </c>
+      <c r="E674" t="n">
+        <v>49301.96</v>
+      </c>
+      <c r="F674" t="n">
+        <v>-11.48</v>
+      </c>
+      <c r="G674" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H674" s="55">
+        <f>E674-G674</f>
+        <v/>
+      </c>
+      <c r="I674" s="34">
+        <f>H674/1000</f>
+        <v/>
+      </c>
+      <c r="J674" s="34">
+        <f>AVERAGE(I673:I674)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3193,7 +3193,7 @@
         <v>47893.42</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>49301.96</v>
+        <v>48341.31</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N674"/>
+  <dimension ref="A1:N675"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28167,22 +28167,22 @@
       <c r="A674" s="62" t="n">
         <v>46307</v>
       </c>
-      <c r="B674" t="n">
+      <c r="B674" s="0" t="n">
         <v>49272.08</v>
       </c>
-      <c r="C674" t="n">
+      <c r="C674" s="0" t="n">
         <v>49412.9</v>
       </c>
-      <c r="D674" t="n">
+      <c r="D674" s="0" t="n">
         <v>48768.82</v>
       </c>
-      <c r="E674" t="n">
+      <c r="E674" s="0" t="n">
         <v>49301.96</v>
       </c>
-      <c r="F674" t="n">
+      <c r="F674" s="0" t="n">
         <v>-11.48</v>
       </c>
-      <c r="G674" t="n">
+      <c r="G674" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H674" s="55">
@@ -28195,6 +28195,41 @@
       </c>
       <c r="J674" s="34">
         <f>AVERAGE(I673:I674)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="62" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B675" t="n">
+        <v>49126.27</v>
+      </c>
+      <c r="C675" t="n">
+        <v>49126.27</v>
+      </c>
+      <c r="D675" t="n">
+        <v>48066.36</v>
+      </c>
+      <c r="E675" t="n">
+        <v>48341.31</v>
+      </c>
+      <c r="F675" t="n">
+        <v>-960.65</v>
+      </c>
+      <c r="G675" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H675" s="55">
+        <f>E675-G675</f>
+        <v/>
+      </c>
+      <c r="I675" s="34">
+        <f>H675/1000</f>
+        <v/>
+      </c>
+      <c r="J675" s="34">
+        <f>AVERAGE(I674:I675)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3193,7 +3193,7 @@
         <v>47893.42</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>48341.31</v>
+        <v>48625.83</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N675"/>
+  <dimension ref="A1:N676"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28202,22 +28202,22 @@
       <c r="A675" s="62" t="n">
         <v>46308</v>
       </c>
-      <c r="B675" t="n">
+      <c r="B675" s="0" t="n">
         <v>49126.27</v>
       </c>
-      <c r="C675" t="n">
+      <c r="C675" s="0" t="n">
         <v>49126.27</v>
       </c>
-      <c r="D675" t="n">
+      <c r="D675" s="0" t="n">
         <v>48066.36</v>
       </c>
-      <c r="E675" t="n">
+      <c r="E675" s="0" t="n">
         <v>48341.31</v>
       </c>
-      <c r="F675" t="n">
+      <c r="F675" s="0" t="n">
         <v>-960.65</v>
       </c>
-      <c r="G675" t="n">
+      <c r="G675" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H675" s="55">
@@ -28230,6 +28230,41 @@
       </c>
       <c r="J675" s="34">
         <f>AVERAGE(I674:I675)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="62" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B676" t="n">
+        <v>48382.64</v>
+      </c>
+      <c r="C676" t="n">
+        <v>49059.12</v>
+      </c>
+      <c r="D676" t="n">
+        <v>48382.64</v>
+      </c>
+      <c r="E676" t="n">
+        <v>48625.83</v>
+      </c>
+      <c r="F676" t="n">
+        <v>284.52</v>
+      </c>
+      <c r="G676" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H676" s="55">
+        <f>E676-G676</f>
+        <v/>
+      </c>
+      <c r="I676" s="34">
+        <f>H676/1000</f>
+        <v/>
+      </c>
+      <c r="J676" s="34">
+        <f>AVERAGE(I675:I676)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3190,10 +3190,10 @@
         <v>49968.92</v>
       </c>
       <c r="E55" s="0" t="n">
-        <v>47893.42</v>
+        <v>46795.38</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>48625.83</v>
+        <v>46969.87</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N676"/>
+  <dimension ref="A1:N677"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28237,22 +28237,22 @@
       <c r="A676" s="62" t="n">
         <v>46309</v>
       </c>
-      <c r="B676" t="n">
+      <c r="B676" s="0" t="n">
         <v>48382.64</v>
       </c>
-      <c r="C676" t="n">
+      <c r="C676" s="0" t="n">
         <v>49059.12</v>
       </c>
-      <c r="D676" t="n">
+      <c r="D676" s="0" t="n">
         <v>48382.64</v>
       </c>
-      <c r="E676" t="n">
+      <c r="E676" s="0" t="n">
         <v>48625.83</v>
       </c>
-      <c r="F676" t="n">
+      <c r="F676" s="0" t="n">
         <v>284.52</v>
       </c>
-      <c r="G676" t="n">
+      <c r="G676" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H676" s="55">
@@ -28265,6 +28265,41 @@
       </c>
       <c r="J676" s="34">
         <f>AVERAGE(I675:I676)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="62" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B677" t="n">
+        <v>48382.75</v>
+      </c>
+      <c r="C677" t="n">
+        <v>48382.75</v>
+      </c>
+      <c r="D677" t="n">
+        <v>46795.38</v>
+      </c>
+      <c r="E677" t="n">
+        <v>46969.87</v>
+      </c>
+      <c r="F677" t="n">
+        <v>-1655.96</v>
+      </c>
+      <c r="G677" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H677" s="55">
+        <f>E677-G677</f>
+        <v/>
+      </c>
+      <c r="I677" s="34">
+        <f>H677/1000</f>
+        <v/>
+      </c>
+      <c r="J677" s="34">
+        <f>AVERAGE(I676:I677)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3193,7 +3193,7 @@
         <v>46795.38</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>46969.87</v>
+        <v>47111.26</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N677"/>
+  <dimension ref="A1:N678"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28272,22 +28272,22 @@
       <c r="A677" s="62" t="n">
         <v>46310</v>
       </c>
-      <c r="B677" t="n">
+      <c r="B677" s="0" t="n">
         <v>48382.75</v>
       </c>
-      <c r="C677" t="n">
+      <c r="C677" s="0" t="n">
         <v>48382.75</v>
       </c>
-      <c r="D677" t="n">
+      <c r="D677" s="0" t="n">
         <v>46795.38</v>
       </c>
-      <c r="E677" t="n">
+      <c r="E677" s="0" t="n">
         <v>46969.87</v>
       </c>
-      <c r="F677" t="n">
+      <c r="F677" s="0" t="n">
         <v>-1655.96</v>
       </c>
-      <c r="G677" t="n">
+      <c r="G677" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H677" s="55">
@@ -28300,6 +28300,41 @@
       </c>
       <c r="J677" s="34">
         <f>AVERAGE(I676:I677)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="62" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B678" t="n">
+        <v>46995.03</v>
+      </c>
+      <c r="C678" t="n">
+        <v>47520.6</v>
+      </c>
+      <c r="D678" t="n">
+        <v>46995.03</v>
+      </c>
+      <c r="E678" t="n">
+        <v>47111.26</v>
+      </c>
+      <c r="F678" t="n">
+        <v>141.39</v>
+      </c>
+      <c r="G678" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H678" s="55">
+        <f>E678-G678</f>
+        <v/>
+      </c>
+      <c r="I678" s="34">
+        <f>H678/1000</f>
+        <v/>
+      </c>
+      <c r="J678" s="34">
+        <f>AVERAGE(I677:I678)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3190,10 +3190,10 @@
         <v>49968.92</v>
       </c>
       <c r="E55" s="0" t="n">
-        <v>46795.38</v>
+        <v>46170</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>47111.26</v>
+        <v>46822.08</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N678"/>
+  <dimension ref="A1:N679"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28307,22 +28307,22 @@
       <c r="A678" s="62" t="n">
         <v>46311</v>
       </c>
-      <c r="B678" t="n">
+      <c r="B678" s="0" t="n">
         <v>46995.03</v>
       </c>
-      <c r="C678" t="n">
+      <c r="C678" s="0" t="n">
         <v>47520.6</v>
       </c>
-      <c r="D678" t="n">
+      <c r="D678" s="0" t="n">
         <v>46995.03</v>
       </c>
-      <c r="E678" t="n">
+      <c r="E678" s="0" t="n">
         <v>47111.26</v>
       </c>
-      <c r="F678" t="n">
+      <c r="F678" s="0" t="n">
         <v>141.39</v>
       </c>
-      <c r="G678" t="n">
+      <c r="G678" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H678" s="55">
@@ -28335,6 +28335,41 @@
       </c>
       <c r="J678" s="34">
         <f>AVERAGE(I677:I678)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="62" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B679" t="n">
+        <v>46844.64</v>
+      </c>
+      <c r="C679" t="n">
+        <v>46844.64</v>
+      </c>
+      <c r="D679" t="n">
+        <v>46170</v>
+      </c>
+      <c r="E679" t="n">
+        <v>46822.08</v>
+      </c>
+      <c r="F679" t="n">
+        <v>-289.18</v>
+      </c>
+      <c r="G679" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H679" s="55">
+        <f>E679-G679</f>
+        <v/>
+      </c>
+      <c r="I679" s="34">
+        <f>H679/1000</f>
+        <v/>
+      </c>
+      <c r="J679" s="34">
+        <f>AVERAGE(I678:I679)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3190,10 +3190,10 @@
         <v>49968.92</v>
       </c>
       <c r="E55" s="0" t="n">
-        <v>46170</v>
+        <v>46163.03</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>46822.08</v>
+        <v>46292.93</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N679"/>
+  <dimension ref="A1:N680"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28342,22 +28342,22 @@
       <c r="A679" s="62" t="n">
         <v>46314</v>
       </c>
-      <c r="B679" t="n">
+      <c r="B679" s="0" t="n">
         <v>46844.64</v>
       </c>
-      <c r="C679" t="n">
+      <c r="C679" s="0" t="n">
         <v>46844.64</v>
       </c>
-      <c r="D679" t="n">
+      <c r="D679" s="0" t="n">
         <v>46170</v>
       </c>
-      <c r="E679" t="n">
+      <c r="E679" s="0" t="n">
         <v>46822.08</v>
       </c>
-      <c r="F679" t="n">
+      <c r="F679" s="0" t="n">
         <v>-289.18</v>
       </c>
-      <c r="G679" t="n">
+      <c r="G679" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H679" s="55">
@@ -28370,6 +28370,41 @@
       </c>
       <c r="J679" s="34">
         <f>AVERAGE(I678:I679)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="62" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B680" t="n">
+        <v>46712.57</v>
+      </c>
+      <c r="C680" t="n">
+        <v>46967.91</v>
+      </c>
+      <c r="D680" t="n">
+        <v>46163.03</v>
+      </c>
+      <c r="E680" t="n">
+        <v>46292.93</v>
+      </c>
+      <c r="F680" t="n">
+        <v>-529.15</v>
+      </c>
+      <c r="G680" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H680" s="55">
+        <f>E680-G680</f>
+        <v/>
+      </c>
+      <c r="I680" s="34">
+        <f>H680/1000</f>
+        <v/>
+      </c>
+      <c r="J680" s="34">
+        <f>AVERAGE(I679:I680)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3193,7 +3193,7 @@
         <v>46163.03</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>46292.93</v>
+        <v>46887.77</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N680"/>
+  <dimension ref="A1:N681"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28377,22 +28377,22 @@
       <c r="A680" s="62" t="n">
         <v>46315</v>
       </c>
-      <c r="B680" t="n">
+      <c r="B680" s="0" t="n">
         <v>46712.57</v>
       </c>
-      <c r="C680" t="n">
+      <c r="C680" s="0" t="n">
         <v>46967.91</v>
       </c>
-      <c r="D680" t="n">
+      <c r="D680" s="0" t="n">
         <v>46163.03</v>
       </c>
-      <c r="E680" t="n">
+      <c r="E680" s="0" t="n">
         <v>46292.93</v>
       </c>
-      <c r="F680" t="n">
+      <c r="F680" s="0" t="n">
         <v>-529.15</v>
       </c>
-      <c r="G680" t="n">
+      <c r="G680" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H680" s="55">
@@ -28405,6 +28405,41 @@
       </c>
       <c r="J680" s="34">
         <f>AVERAGE(I679:I680)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="62" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B681" t="n">
+        <v>46454.33</v>
+      </c>
+      <c r="C681" t="n">
+        <v>47254.93</v>
+      </c>
+      <c r="D681" t="n">
+        <v>46454.33</v>
+      </c>
+      <c r="E681" t="n">
+        <v>46887.77</v>
+      </c>
+      <c r="F681" t="n">
+        <v>594.84</v>
+      </c>
+      <c r="G681" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H681" s="55">
+        <f>E681-G681</f>
+        <v/>
+      </c>
+      <c r="I681" s="34">
+        <f>H681/1000</f>
+        <v/>
+      </c>
+      <c r="J681" s="34">
+        <f>AVERAGE(I680:I681)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3190,10 +3190,10 @@
         <v>49968.92</v>
       </c>
       <c r="E55" s="0" t="n">
-        <v>46163.03</v>
+        <v>46041.43</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>46887.77</v>
+        <v>46041.43</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N681"/>
+  <dimension ref="A1:N682"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28412,22 +28412,22 @@
       <c r="A681" s="62" t="n">
         <v>46316</v>
       </c>
-      <c r="B681" t="n">
+      <c r="B681" s="0" t="n">
         <v>46454.33</v>
       </c>
-      <c r="C681" t="n">
+      <c r="C681" s="0" t="n">
         <v>47254.93</v>
       </c>
-      <c r="D681" t="n">
+      <c r="D681" s="0" t="n">
         <v>46454.33</v>
       </c>
-      <c r="E681" t="n">
+      <c r="E681" s="0" t="n">
         <v>46887.77</v>
       </c>
-      <c r="F681" t="n">
+      <c r="F681" s="0" t="n">
         <v>594.84</v>
       </c>
-      <c r="G681" t="n">
+      <c r="G681" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H681" s="55">
@@ -28440,6 +28440,41 @@
       </c>
       <c r="J681" s="34">
         <f>AVERAGE(I680:I681)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="62" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B682" t="n">
+        <v>46942.75</v>
+      </c>
+      <c r="C682" t="n">
+        <v>47332.18</v>
+      </c>
+      <c r="D682" t="n">
+        <v>46041.43</v>
+      </c>
+      <c r="E682" t="n">
+        <v>46041.43</v>
+      </c>
+      <c r="F682" t="n">
+        <v>-846.34</v>
+      </c>
+      <c r="G682" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H682" s="55">
+        <f>E682-G682</f>
+        <v/>
+      </c>
+      <c r="I682" s="34">
+        <f>H682/1000</f>
+        <v/>
+      </c>
+      <c r="J682" s="34">
+        <f>AVERAGE(I681:I682)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,11 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -28447,22 +28446,22 @@
       <c r="A682" s="62" t="n">
         <v>46317</v>
       </c>
-      <c r="B682" t="n">
+      <c r="B682" s="0" t="n">
         <v>46942.75</v>
       </c>
-      <c r="C682" t="n">
+      <c r="C682" s="0" t="n">
         <v>47332.18</v>
       </c>
-      <c r="D682" t="n">
+      <c r="D682" s="0" t="n">
         <v>46041.43</v>
       </c>
-      <c r="E682" t="n">
+      <c r="E682" s="0" t="n">
         <v>46041.43</v>
       </c>
-      <c r="F682" t="n">
+      <c r="F682" s="0" t="n">
         <v>-846.34</v>
       </c>
-      <c r="G682" t="n">
+      <c r="G682" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H682" s="55">

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy/mm/dd"/>
     <numFmt numFmtId="166" formatCode="YYYY/MM/DD"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -3180,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3189,10 +3190,10 @@
         <v>49968.92</v>
       </c>
       <c r="E55" s="0" t="n">
-        <v>46041.43</v>
+        <v>45676.67</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>46041.43</v>
+        <v>46096.23</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3224,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N682"/>
+  <dimension ref="A1:N683"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28477,6 +28478,41 @@
         <v/>
       </c>
     </row>
+    <row r="683">
+      <c r="A683" s="62" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B683" t="n">
+        <v>46211.2</v>
+      </c>
+      <c r="C683" t="n">
+        <v>46585.45</v>
+      </c>
+      <c r="D683" t="n">
+        <v>45676.67</v>
+      </c>
+      <c r="E683" t="n">
+        <v>46096.23</v>
+      </c>
+      <c r="F683" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G683" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H683" s="55">
+        <f>E683-G683</f>
+        <v/>
+      </c>
+      <c r="I683" s="34">
+        <f>H683/1000</f>
+        <v/>
+      </c>
+      <c r="J683" s="34">
+        <f>AVERAGE(I682:I683)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3193,7 +3193,7 @@
         <v>45676.67</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>46096.23</v>
+        <v>47035.58</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N683"/>
+  <dimension ref="A1:N684"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28482,22 +28482,22 @@
       <c r="A683" s="62" t="n">
         <v>46322</v>
       </c>
-      <c r="B683" t="n">
+      <c r="B683" s="0" t="n">
         <v>46211.2</v>
       </c>
-      <c r="C683" t="n">
+      <c r="C683" s="0" t="n">
         <v>46585.45</v>
       </c>
-      <c r="D683" t="n">
+      <c r="D683" s="0" t="n">
         <v>45676.67</v>
       </c>
-      <c r="E683" t="n">
+      <c r="E683" s="0" t="n">
         <v>46096.23</v>
       </c>
-      <c r="F683" t="n">
+      <c r="F683" s="0" t="n">
         <v>54.8</v>
       </c>
-      <c r="G683" t="n">
+      <c r="G683" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H683" s="55">
@@ -28510,6 +28510,41 @@
       </c>
       <c r="J683" s="34">
         <f>AVERAGE(I682:I683)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="62" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B684" t="n">
+        <v>46402.79</v>
+      </c>
+      <c r="C684" t="n">
+        <v>47060.46</v>
+      </c>
+      <c r="D684" t="n">
+        <v>46402.79</v>
+      </c>
+      <c r="E684" t="n">
+        <v>47035.58</v>
+      </c>
+      <c r="F684" t="n">
+        <v>939.35</v>
+      </c>
+      <c r="G684" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H684" s="55">
+        <f>E684-G684</f>
+        <v/>
+      </c>
+      <c r="I684" s="34">
+        <f>H684/1000</f>
+        <v/>
+      </c>
+      <c r="J684" s="34">
+        <f>AVERAGE(I683:I684)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3193,7 +3193,7 @@
         <v>45676.67</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>47035.58</v>
+        <v>46368.33</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N684"/>
+  <dimension ref="A1:N685"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28517,22 +28517,22 @@
       <c r="A684" s="62" t="n">
         <v>46323</v>
       </c>
-      <c r="B684" t="n">
+      <c r="B684" s="0" t="n">
         <v>46402.79</v>
       </c>
-      <c r="C684" t="n">
+      <c r="C684" s="0" t="n">
         <v>47060.46</v>
       </c>
-      <c r="D684" t="n">
+      <c r="D684" s="0" t="n">
         <v>46402.79</v>
       </c>
-      <c r="E684" t="n">
+      <c r="E684" s="0" t="n">
         <v>47035.58</v>
       </c>
-      <c r="F684" t="n">
+      <c r="F684" s="0" t="n">
         <v>939.35</v>
       </c>
-      <c r="G684" t="n">
+      <c r="G684" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H684" s="55">
@@ -28545,6 +28545,41 @@
       </c>
       <c r="J684" s="34">
         <f>AVERAGE(I683:I684)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="62" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B685" t="n">
+        <v>47014.87</v>
+      </c>
+      <c r="C685" t="n">
+        <v>47015.45</v>
+      </c>
+      <c r="D685" t="n">
+        <v>46055.07</v>
+      </c>
+      <c r="E685" t="n">
+        <v>46368.33</v>
+      </c>
+      <c r="F685" t="n">
+        <v>-667.25</v>
+      </c>
+      <c r="G685" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H685" s="55">
+        <f>E685-G685</f>
+        <v/>
+      </c>
+      <c r="I685" s="34">
+        <f>H685/1000</f>
+        <v/>
+      </c>
+      <c r="J685" s="34">
+        <f>AVERAGE(I684:I685)</f>
         <v/>
       </c>
     </row>

--- a/日開收盤價_更新.xlsx
+++ b/日開收盤價_更新.xlsx
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B55" s="0" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>47961.98</v>
@@ -3190,19 +3190,19 @@
         <v>49968.92</v>
       </c>
       <c r="E55" s="0" t="n">
-        <v>45676.67</v>
+        <v>44726.26</v>
       </c>
       <c r="F55" s="0" t="n">
-        <v>46368.33</v>
+        <v>45211.83</v>
       </c>
       <c r="G55" s="0" t="n">
         <v>49968.92</v>
       </c>
       <c r="H55" s="0" t="n">
-        <v>45398.43</v>
+        <v>44726.26</v>
       </c>
       <c r="I55" s="0" t="n">
-        <v>47683.675</v>
+        <v>47347.59</v>
       </c>
       <c r="J55" s="0" t="n">
         <v>45690.975</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="56">
       <c r="J56" s="0" t="n">
-        <v>47683.675</v>
+        <v>47347.59</v>
       </c>
     </row>
   </sheetData>
@@ -3225,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N685"/>
+  <dimension ref="A1:N686"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col width="10.625" customWidth="1" style="22" min="1" max="1"/>
@@ -28552,22 +28552,22 @@
       <c r="A685" s="62" t="n">
         <v>46324</v>
       </c>
-      <c r="B685" t="n">
+      <c r="B685" s="0" t="n">
         <v>47014.87</v>
       </c>
-      <c r="C685" t="n">
+      <c r="C685" s="0" t="n">
         <v>47015.45</v>
       </c>
-      <c r="D685" t="n">
+      <c r="D685" s="0" t="n">
         <v>46055.07</v>
       </c>
-      <c r="E685" t="n">
+      <c r="E685" s="0" t="n">
         <v>46368.33</v>
       </c>
-      <c r="F685" t="n">
+      <c r="F685" s="0" t="n">
         <v>-667.25</v>
       </c>
-      <c r="G685" t="n">
+      <c r="G685" s="0" t="n">
         <v>45690.975</v>
       </c>
       <c r="H685" s="55">
@@ -28580,6 +28580,41 @@
       </c>
       <c r="J685" s="34">
         <f>AVERAGE(I684:I685)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="62" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B686" t="n">
+        <v>46139.79</v>
+      </c>
+      <c r="C686" t="n">
+        <v>46139.79</v>
+      </c>
+      <c r="D686" t="n">
+        <v>44726.26</v>
+      </c>
+      <c r="E686" t="n">
+        <v>45211.83</v>
+      </c>
+      <c r="F686" t="n">
+        <v>-1156.5</v>
+      </c>
+      <c r="G686" t="n">
+        <v>45690.975</v>
+      </c>
+      <c r="H686" s="55">
+        <f>E686-G686</f>
+        <v/>
+      </c>
+      <c r="I686" s="34">
+        <f>H686/1000</f>
+        <v/>
+      </c>
+      <c r="J686" s="34">
+        <f>AVERAGE(I685:I686)</f>
         <v/>
       </c>
     </row>
